--- a/results/archive/result-tables.xlsx
+++ b/results/archive/result-tables.xlsx
@@ -9,12 +9,13 @@
     <sheet name="Table2" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Table3" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Table4" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Table5" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="1365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1876" uniqueCount="1876">
   <si>
     <t xml:space="preserve">scenario</t>
   </si>
@@ -1840,6 +1841,30 @@
     <t xml:space="preserve">73 (68.6, 78.6)</t>
   </si>
   <si>
+    <t xml:space="preserve">60.7 (56.9, 64.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.1 (58.8, 65.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1 (12.6, 14.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">70.9 (66.6, 74)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">63.7 (59, 67.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">65.8 (60.8, 68.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1 (8.8, 9.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">73.1 (68.3, 76.7)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CInc</t>
   </si>
   <si>
@@ -3430,6 +3455,30 @@
     <t xml:space="preserve">0.2 (0, 0.6)</t>
   </si>
   <si>
+    <t xml:space="preserve">113.8 (107.5, 126)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6 (6.4, 24.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1 (4.8, 18.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2 (0.1, 5.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2 (12.1, 14.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 (2, 4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5 (12.3, 25.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (0.1, 0.6)</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDeaths</t>
   </si>
   <si>
@@ -4109,6 +4158,1491 @@
   </si>
   <si>
     <t xml:space="preserve">14.9 (8.2, 23.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.284 (0.264, 0.298)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06 (0.046, 0.08)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5 (13.3, 23.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCase</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaseAverted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CCaseWork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CaseAvertedWork</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4 (92.2, 101.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-6.2, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-6.5, 3.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.9, -1.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.3 (96.9, 106.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-5.1, 4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-5, 4.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.9, -1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">116.9 (113.9, 122.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.5 (-26.7, -18.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-22.5 (-28, -19.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (0.3, 0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">126.6 (123.2, 131.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-25.3 (-30.6, -22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-25 (-30.2, -21.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">112.8 (111.8, 114.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.3 (-19.3, -16.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-18.2 (-20.2, -17.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.1 (121.1, 123.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.8 (-22.2, -19.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.5 (-21.9, -19.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.9 (108.8, 111.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-14.4 (-16.5, -13.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.1 (-17.3, -14)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">118.7 (117.3, 120.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.5 (-19.6, -16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.2 (-19.3, -15.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.4 (107.5, 109.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13 (-14, -12.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.6 (-14.7, -12.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (0.4, 0.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">117.1 (115.7, 118.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.8 (-17, -14.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-15.6 (-16.8, -14.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.4 (105.5, 107.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11 (-12.5, -10.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.5 (-13.1, -10.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">114.9 (113.3, 116.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.6 (-15.1, -12)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-13.4 (-14.9, -11.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (0.5, 0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.1 (101.7, 104.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.6 (-8.8, -6.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8 (-9.2, -6.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111 (108.5, 112.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.7 (-11.4, -7.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.6 (-11.3, -7.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7 (0.5, 0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99 (96.9, 104.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.5 (-9, -1.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.7 (-9.4, -1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-0.1, 0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.4 (102.4, 109.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.1 (-8.5, -1.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5 (-8.4, -1.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (-0.1, 1.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8 (92, 98.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4 (-3.2, 3.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4 (-3.4, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102 (97.4, 104.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-3.6, 3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-3.5, 3.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.9, -1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.4 (90.8, 97.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (-1.7, 4.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (-1.8, 4.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.3 (-3.5, 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.3 (95.1, 103.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 (-2.6, 6.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.4 (-2.9, -0.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">89.9 (84.6, 101.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.5 (-6, 10.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8 (-6.3, 11.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (-0.4, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1 (88.4, 104.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2 (-3.4, 12.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1 (-3.4, 12.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (-0.4, 2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.1 (82.1, 89.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3 (5.8, 13.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8 (6, 13.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 (0.4, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">90.7 (85.2, 94.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5 (6.4, 16)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4 (6.3, 15.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 (0.4, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1 (80.4, 91.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3 (3.8, 15)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8 (4, 15.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7 (0.1, 1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">88.8 (83.3, 94.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5 (7, 18)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3 (6.9, 17.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 (0.2, 2.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77.8 (74.1, 82)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6 (13.4, 21.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5 (14.1, 22.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 (0.6, 1.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.1 (76.4, 86.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2 (14.7, 24.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9 (14.5, 24.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 (0.7, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113.3 (111.5, 115.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-17.8 (-20.1, -16.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-18.7 (-21.1, -16.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">122.4 (120.5, 124.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.1 (-23.1, -19.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.8 (-22.8, -19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4 (91.7, 98.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (-3.3, 3.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (-3.4, 3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.8, -1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.1 (97.6, 105.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-4.4, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-4.3, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.9, -1.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3 (92.5, 98.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-3.4, 2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-3.6, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.9 (97.3, 104.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.6 (-3.4, 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-2, -1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5 (92.3, 101)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-5.6, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-5.8, 3.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.1 (97.6, 106.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (-4.8, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (-4.7, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6 (92.4, 101.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-6, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-6.2, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102 (98.1, 106.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-5.7, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-5.6, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.3 (92.8, 104.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-8.8, 2.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-9.2, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103 (98.1, 109.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-8.3, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-8.2, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8 (92.4, 104.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4 (-8.7, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4 (-9.1, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.1 (98.2, 109.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-8.4, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-8.3, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9 (92.4, 108)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-12.5, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-13.1, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.5 (97.3, 114.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.2 (-12.8, 3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.2 (-12.6, 3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.8, -1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3 (92.4, 98.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (-2.7, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1 (-2.8, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.8 (97.6, 104.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-3.3, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.6 (-1.8, -1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5 (92, 103.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-8.4, 3.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-8.8, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.2 (97.7, 108.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 (-7.3, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-7.2, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.8 (93.1, 101.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4 (-5.8, 2.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.4 (-6.1, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102 (98.3, 106.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-5, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-4.9, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.8, -1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1 (91.9, 103.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-8.5, 3.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-8.9, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.3 (97.1, 108.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-7.3, 4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-7.2, 4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5 (92.7, 98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-2.6, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-2.7, 2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.8 (98.3, 105)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-3.7, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9 (91.6, 104.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-8.8, 3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-9.2, 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.2 (97, 108.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-7.6, 4.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-7.5, 4.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.5 (91.6, 97.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.9 (-1.8, 3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (-1.9, 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.8 (97, 104.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (-2.8, 4.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.6 (92.3, 102.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2 (-6.8, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2 (-7.1, 3.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.8, -1.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.8 (97.9, 106.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-5.1, 3.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-5.1, 3.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.1 (92.7, 98)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-2.6, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-2.7, 2.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.6 (98.2, 104.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3 (-3.5, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3 (-3.4, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.7 (92.1, 98.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.7 (-2.7, 3.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.8 (-2.8, 3.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9 (97.7, 104.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-3.5, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-3.4, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9 (91.3, 98.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (-2.8, 4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (-3, 4.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101 (96.1, 105.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-3.9, 5.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2 (92.8, 98.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-2.7, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-2.8, 2.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.8 (-2, -1.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9 (97.6, 105)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-3.8, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.3 (-3.7, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-2, -1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2 (92.3, 98.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-2.8, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-2.9, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9 (97.6, 105.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-4, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-4, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96 (92.8, 98.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-3.3, 2.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.6 (-3.5, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102 (98.3, 105.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-4.4, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-4.3, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.8, -1.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.5 (93, 98.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-3.4, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-3.6, 2.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.1 (98.2, 104.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-3.1, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-3.1, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97 (93.5, 108.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.6 (-13.3, 1.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-13.9, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.9 (98.2, 114.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.6 (-13.1, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.6 (-13, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.2 (92.8, 103.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-7.8, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-8.2, 2.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.1 (97.3, 107.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-6.4, 4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.8 (-6.3, 3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5 (94, 110.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 (-14.7, 1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.1 (-15.4, 1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.5 (99.3, 115)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.2 (-13.8, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.2 (-13.6, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.4 (92.9, 98.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-2.8, 2.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 (-2.9, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.3 (98.2, 105.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-4, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-3.9, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.8 (-1.9, -1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.4 (93.1, 102.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 (-6.7, 2.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 (-7, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.2 (98.8, 107.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.9 (-5.9, 2.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.9 (-5.8, 2.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.1 (92.8, 101.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-5.9, 2.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-6.2, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.3 (98.2, 106.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1 (-4.8, 3.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.9 (93.1, 98.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-3, 2.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.5 (-3.1, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.2 (98.5, 105.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-3.9, 2.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.9 (-3.8, 2.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94.9 (91.8, 97.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.5 (-2.2, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.6 (-2.3, 3.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9 (96.8, 103.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-2.6, 4.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-2.6, 4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.1 (92.7, 107.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-12.4, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.7 (-13, 2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.7 (97.6, 113.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.5 (-12.1, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.4 (-11.9, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95 (91.9, 100.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-5.3, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.4 (-5.5, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.4 (96.6, 105.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-4.6, 4.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-4.6, 4.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96 (93.1, 104.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.6 (-8.7, 2.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.6 (-9.1, 2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.6 (99.2, 109.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.3 (-8, 2.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.3 (-7.9, 2.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.7 (87.1, 102.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8 (-7.2, 8.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (-7.6, 8.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.3 (91.7, 107)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4 (-5.8, 9.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9 (-5.7, 9.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.1 (89.3, 104.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3 (-8.9, 6.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4 (-9.4, 6.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.5 (94.5, 109)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7 (-7.8, 6.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7 (-7.7, 6.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.7 (89.8, 96.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7 (-1.1, 5.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8 (-1.1, 5.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.1 (94.8, 103.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 (-2.1, 6.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.3 (91.9, 100.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-4.8, 3.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-5.1, 3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.4 (96.8, 106.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-4.8, 4.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1 (-4.7, 4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.8 (-1.9, -1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97 (93.9, 104)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.6 (-8.5, 1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.6 (-8.9, 1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.1 (99.9, 109.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.9 (-8.4, 1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.8 (-8.3, 1.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.6 (94.7, 100)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.2 (-4.6, 0.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.3 (-4.8, 0.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.4 (100.7, 107.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.2 (-6.3, 0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.1 (-6.2, 0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8 (96.4, 100.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.4 (-5.3, -1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.5 (-5.5, -1.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">105.4 (102.7, 108)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.1 (-6.7, -1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.1 (-6.6, -1.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.1 (97.5, 101.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.7 (-5.9, -2.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.9 (-6.2, -2.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.7, -1.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">107.3 (104.2, 109.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6 (-8.1, -2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6 (-8, -2.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100.9 (99.3, 102.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.5 (-7, -3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.7 (-7.3, -4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">108.2 (105.7, 110)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.9 (-8.8, -4.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.8 (-8.7, -4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.4 (99.8, 102.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6 (-7.4, -4.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.2 (-7.8, -4.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.1 (106.6, 111.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.8 (-9.9, -5.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.7 (-9.8, -5.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.1 (101.6, 104.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.6 (-8.8, -6.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8 (-9.2, -6.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">110.7 (108.9, 112.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.4 (-11.5, -7.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.3 (-11.4, -7.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.1 (86.9, 102.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4 (-6.7, 8.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6 (-7, 8.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8 (91.5, 106.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5 (-4.9, 9.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5 (-4.9, 9.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92.2 (88.3, 94.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3 (1.1, 7.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4 (1.2, 7.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">97.7 (93, 101.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5 (-0.2, 8.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5 (-0.2, 8.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">93.8 (90.8, 99.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6 (-4.2, 4.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.7 (-4.4, 4.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.8 (95.3, 104.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 (-3.4, 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 (-3.4, 5.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95.2 (92.4, 98.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-3.5, 3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.2 (-3.7, 3.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.9 (97.6, 105.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.6 (-4.3, 3.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.9 (93.5, 100.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.4 (-4.7, 1.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.5 (-4.9, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.8 (99.8, 107.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.5 (-6.2, 1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2.5 (-6.1, 1.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.8 (96.1, 101.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.4 (-5.6, -0.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3.5 (-5.9, -0.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106 (101.9, 108.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.7 (-7.3, -0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.6 (-7.2, -0.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">99.5 (97.7, 101.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4 (-6.4, -2.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-4.2 (-6.7, -2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">106.7 (103.7, 109.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.4 (-8.2, -2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5.3 (-8.1, -2.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">101.5 (99.1, 103.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.1 (-7.7, -3.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.4 (-8, -3.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.3 (105.4, 111.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8 (-10.1, -4.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.9 (-9.9, -4.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.3 (100.4, 103.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6.9 (-7.9, -5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7.2 (-8.3, -5.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">109.6 (107.2, 111.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.3 (-10, -6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.2 (-9.8, -5.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">103.7 (102.1, 104.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.2 (-9.4, -6.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-8.6 (-9.9, -6.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1.7 (-1.7, -1.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.8 (108.9, 113.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.5 (-12, -7.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-10.4 (-11.8, -7.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">104.7 (103.5, 105.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.3 (-10.2, -8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9.8 (-10.7, -8.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">113 (110.8, 114.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.7 (-13.1, -9.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-11.6 (-13, -9.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">115.8 (113.8, 118.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-20.4 (-23.5, -18.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-21.3 (-24.6, -19.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.5 (123.5, 128.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-24.3 (-27.2, -22.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-24 (-26.8, -21.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.3 (31.5, 45.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38 (33, 47.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8 (-1.8, 6.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4 (35.7, 51.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.8 (35.2, 51)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3 (-1.9, 6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2 (82.1, 90.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2 (4.5, 13.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7 (4.7, 13.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 (0.3, 2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91 (85.8, 96.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2 (5.2, 15.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1 (5.1, 15.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 (0.3, 2.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.8 (77.9, 89.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6 (6, 17.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2 (6.3, 18.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.4 (0.3, 3.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">87.3 (81.1, 92.7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9 (8.5, 20.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8 (8.4, 19.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.3 (0.2, 3.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8 (76.4, 87.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7 (7.8, 19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3 (8.2, 19.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6 (0.2, 4.3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">85.1 (79, 91.1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2 (10.2, 22.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 (10.1, 22)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.2 (0.1, 3.4)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81 (75.8, 85.9)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4 (9.5, 19.6)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1 (10, 20.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9 (0.5, 3.8)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">84.9 (78.8, 89.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4 (12, 22.5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2 (11.9, 22.2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.5 (0.2, 3.5)</t>
   </si>
 </sst>
 </file>
@@ -7101,16 +8635,36 @@
       <c r="A77" t="n">
         <v>75</v>
       </c>
-      <c r="B77"/>
-      <c r="C77"/>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
-      <c r="J77"/>
-      <c r="K77"/>
+      <c r="B77" t="s">
+        <v>608</v>
+      </c>
+      <c r="C77" t="s">
+        <v>77</v>
+      </c>
+      <c r="D77" t="s">
+        <v>609</v>
+      </c>
+      <c r="E77" t="s">
+        <v>610</v>
+      </c>
+      <c r="F77" t="s">
+        <v>611</v>
+      </c>
+      <c r="G77" t="s">
+        <v>612</v>
+      </c>
+      <c r="H77" t="s">
+        <v>95</v>
+      </c>
+      <c r="I77" t="s">
+        <v>613</v>
+      </c>
+      <c r="J77" t="s">
+        <v>614</v>
+      </c>
+      <c r="K77" t="s">
+        <v>615</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7128,28 +8682,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="C1" t="s">
-        <v>609</v>
+        <v>617</v>
       </c>
       <c r="D1" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="E1" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="F1" t="s">
-        <v>612</v>
+        <v>620</v>
       </c>
       <c r="G1" t="s">
-        <v>613</v>
+        <v>621</v>
       </c>
       <c r="H1" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="I1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2">
@@ -7157,28 +8711,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>616</v>
+        <v>624</v>
       </c>
       <c r="C2" t="s">
-        <v>617</v>
+        <v>625</v>
       </c>
       <c r="D2" t="s">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="E2" t="s">
-        <v>619</v>
+        <v>627</v>
       </c>
       <c r="F2" t="s">
-        <v>620</v>
+        <v>628</v>
       </c>
       <c r="G2" t="s">
-        <v>621</v>
+        <v>629</v>
       </c>
       <c r="H2" t="s">
-        <v>622</v>
+        <v>630</v>
       </c>
       <c r="I2" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="3">
@@ -7186,28 +8740,28 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>624</v>
+        <v>632</v>
       </c>
       <c r="C3" t="s">
-        <v>625</v>
+        <v>633</v>
       </c>
       <c r="D3" t="s">
-        <v>626</v>
+        <v>634</v>
       </c>
       <c r="E3" t="s">
-        <v>627</v>
+        <v>635</v>
       </c>
       <c r="F3" t="s">
-        <v>628</v>
+        <v>636</v>
       </c>
       <c r="G3" t="s">
-        <v>629</v>
+        <v>637</v>
       </c>
       <c r="H3" t="s">
-        <v>630</v>
+        <v>638</v>
       </c>
       <c r="I3" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="4">
@@ -7215,28 +8769,28 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>632</v>
+        <v>640</v>
       </c>
       <c r="C4" t="s">
-        <v>633</v>
+        <v>641</v>
       </c>
       <c r="D4" t="s">
-        <v>634</v>
+        <v>642</v>
       </c>
       <c r="E4" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="F4" t="s">
-        <v>636</v>
+        <v>644</v>
       </c>
       <c r="G4" t="s">
-        <v>637</v>
+        <v>645</v>
       </c>
       <c r="H4" t="s">
-        <v>638</v>
+        <v>646</v>
       </c>
       <c r="I4" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="5">
@@ -7244,28 +8798,28 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>647</v>
+      </c>
+      <c r="C5" t="s">
+        <v>648</v>
+      </c>
+      <c r="D5" t="s">
+        <v>649</v>
+      </c>
+      <c r="E5" t="s">
+        <v>635</v>
+      </c>
+      <c r="F5" t="s">
+        <v>650</v>
+      </c>
+      <c r="G5" t="s">
+        <v>651</v>
+      </c>
+      <c r="H5" t="s">
+        <v>652</v>
+      </c>
+      <c r="I5" t="s">
         <v>639</v>
-      </c>
-      <c r="C5" t="s">
-        <v>640</v>
-      </c>
-      <c r="D5" t="s">
-        <v>641</v>
-      </c>
-      <c r="E5" t="s">
-        <v>627</v>
-      </c>
-      <c r="F5" t="s">
-        <v>642</v>
-      </c>
-      <c r="G5" t="s">
-        <v>643</v>
-      </c>
-      <c r="H5" t="s">
-        <v>644</v>
-      </c>
-      <c r="I5" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="6">
@@ -7273,28 +8827,28 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>645</v>
+        <v>653</v>
       </c>
       <c r="C6" t="s">
-        <v>646</v>
+        <v>654</v>
       </c>
       <c r="D6" t="s">
-        <v>647</v>
+        <v>655</v>
       </c>
       <c r="E6" t="s">
-        <v>648</v>
+        <v>656</v>
       </c>
       <c r="F6" t="s">
-        <v>649</v>
+        <v>657</v>
       </c>
       <c r="G6" t="s">
-        <v>650</v>
+        <v>658</v>
       </c>
       <c r="H6" t="s">
-        <v>651</v>
+        <v>659</v>
       </c>
       <c r="I6" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="7">
@@ -7302,28 +8856,28 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>652</v>
+        <v>660</v>
       </c>
       <c r="C7" t="s">
-        <v>653</v>
+        <v>661</v>
       </c>
       <c r="D7" t="s">
-        <v>654</v>
+        <v>662</v>
       </c>
       <c r="E7" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="F7" t="s">
-        <v>656</v>
+        <v>664</v>
       </c>
       <c r="G7" t="s">
-        <v>657</v>
+        <v>665</v>
       </c>
       <c r="H7" t="s">
-        <v>658</v>
+        <v>666</v>
       </c>
       <c r="I7" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="8">
@@ -7331,28 +8885,28 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>659</v>
+        <v>667</v>
       </c>
       <c r="C8" t="s">
-        <v>660</v>
+        <v>668</v>
       </c>
       <c r="D8" t="s">
-        <v>661</v>
+        <v>669</v>
       </c>
       <c r="E8" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
       <c r="F8" t="s">
-        <v>662</v>
+        <v>670</v>
       </c>
       <c r="G8" t="s">
-        <v>663</v>
+        <v>671</v>
       </c>
       <c r="H8" t="s">
-        <v>664</v>
+        <v>672</v>
       </c>
       <c r="I8" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="9">
@@ -7360,28 +8914,28 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>665</v>
+        <v>673</v>
       </c>
       <c r="C9" t="s">
-        <v>666</v>
+        <v>674</v>
       </c>
       <c r="D9" t="s">
-        <v>667</v>
+        <v>675</v>
       </c>
       <c r="E9" t="s">
-        <v>668</v>
+        <v>676</v>
       </c>
       <c r="F9" t="s">
-        <v>669</v>
+        <v>677</v>
       </c>
       <c r="G9" t="s">
-        <v>670</v>
+        <v>678</v>
       </c>
       <c r="H9" t="s">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="I9" t="s">
-        <v>672</v>
+        <v>680</v>
       </c>
     </row>
     <row r="10">
@@ -7389,28 +8943,28 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>673</v>
+        <v>681</v>
       </c>
       <c r="C10" t="s">
-        <v>674</v>
+        <v>682</v>
       </c>
       <c r="D10" t="s">
-        <v>675</v>
+        <v>683</v>
       </c>
       <c r="E10" t="s">
-        <v>676</v>
+        <v>684</v>
       </c>
       <c r="F10" t="s">
-        <v>677</v>
+        <v>685</v>
       </c>
       <c r="G10" t="s">
-        <v>678</v>
+        <v>686</v>
       </c>
       <c r="H10" t="s">
-        <v>679</v>
+        <v>687</v>
       </c>
       <c r="I10" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="11">
@@ -7418,28 +8972,28 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>680</v>
+        <v>688</v>
       </c>
       <c r="C11" t="s">
-        <v>681</v>
+        <v>689</v>
       </c>
       <c r="D11" t="s">
-        <v>682</v>
+        <v>690</v>
       </c>
       <c r="E11" t="s">
-        <v>683</v>
+        <v>691</v>
       </c>
       <c r="F11" t="s">
-        <v>684</v>
+        <v>692</v>
       </c>
       <c r="G11" t="s">
-        <v>685</v>
+        <v>693</v>
       </c>
       <c r="H11" t="s">
-        <v>686</v>
+        <v>694</v>
       </c>
       <c r="I11" t="s">
-        <v>687</v>
+        <v>695</v>
       </c>
     </row>
     <row r="12">
@@ -7447,28 +9001,28 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>688</v>
+        <v>696</v>
       </c>
       <c r="C12" t="s">
-        <v>689</v>
+        <v>697</v>
       </c>
       <c r="D12" t="s">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="E12" t="s">
-        <v>691</v>
+        <v>699</v>
       </c>
       <c r="F12" t="s">
-        <v>692</v>
+        <v>700</v>
       </c>
       <c r="G12" t="s">
-        <v>693</v>
+        <v>701</v>
       </c>
       <c r="H12" t="s">
-        <v>694</v>
+        <v>702</v>
       </c>
       <c r="I12" t="s">
-        <v>695</v>
+        <v>703</v>
       </c>
     </row>
     <row r="13">
@@ -7476,28 +9030,28 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="C13" t="s">
-        <v>697</v>
+        <v>705</v>
       </c>
       <c r="D13" t="s">
-        <v>698</v>
+        <v>706</v>
       </c>
       <c r="E13" t="s">
-        <v>699</v>
+        <v>707</v>
       </c>
       <c r="F13" t="s">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="G13" t="s">
-        <v>701</v>
+        <v>709</v>
       </c>
       <c r="H13" t="s">
-        <v>702</v>
+        <v>710</v>
       </c>
       <c r="I13" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
     </row>
     <row r="14">
@@ -7505,28 +9059,28 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>704</v>
+        <v>712</v>
       </c>
       <c r="C14" t="s">
-        <v>705</v>
+        <v>713</v>
       </c>
       <c r="D14" t="s">
-        <v>706</v>
+        <v>714</v>
       </c>
       <c r="E14" t="s">
-        <v>707</v>
+        <v>715</v>
       </c>
       <c r="F14" t="s">
-        <v>708</v>
+        <v>716</v>
       </c>
       <c r="G14" t="s">
-        <v>709</v>
+        <v>717</v>
       </c>
       <c r="H14" t="s">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="I14" t="s">
-        <v>711</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15">
@@ -7534,28 +9088,28 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>712</v>
+        <v>720</v>
       </c>
       <c r="C15" t="s">
-        <v>713</v>
+        <v>721</v>
       </c>
       <c r="D15" t="s">
-        <v>714</v>
+        <v>722</v>
       </c>
       <c r="E15" t="s">
-        <v>715</v>
+        <v>723</v>
       </c>
       <c r="F15" t="s">
-        <v>716</v>
+        <v>724</v>
       </c>
       <c r="G15" t="s">
-        <v>717</v>
+        <v>725</v>
       </c>
       <c r="H15" t="s">
-        <v>718</v>
+        <v>726</v>
       </c>
       <c r="I15" t="s">
-        <v>703</v>
+        <v>711</v>
       </c>
     </row>
     <row r="16">
@@ -7563,28 +9117,28 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>719</v>
+        <v>727</v>
       </c>
       <c r="C16" t="s">
-        <v>720</v>
+        <v>728</v>
       </c>
       <c r="D16" t="s">
-        <v>721</v>
+        <v>729</v>
       </c>
       <c r="E16" t="s">
-        <v>635</v>
+        <v>643</v>
       </c>
       <c r="F16" t="s">
-        <v>722</v>
+        <v>730</v>
       </c>
       <c r="G16" t="s">
-        <v>723</v>
+        <v>731</v>
       </c>
       <c r="H16" t="s">
-        <v>724</v>
+        <v>732</v>
       </c>
       <c r="I16" t="s">
-        <v>631</v>
+        <v>639</v>
       </c>
     </row>
     <row r="17">
@@ -7592,28 +9146,28 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>725</v>
+        <v>733</v>
       </c>
       <c r="C17" t="s">
-        <v>726</v>
+        <v>734</v>
       </c>
       <c r="D17" t="s">
-        <v>727</v>
+        <v>735</v>
       </c>
       <c r="E17" t="s">
-        <v>728</v>
+        <v>736</v>
       </c>
       <c r="F17" t="s">
-        <v>729</v>
+        <v>737</v>
       </c>
       <c r="G17" t="s">
-        <v>730</v>
+        <v>738</v>
       </c>
       <c r="H17" t="s">
-        <v>731</v>
+        <v>739</v>
       </c>
       <c r="I17" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="18">
@@ -7621,28 +9175,28 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="C18" t="s">
-        <v>733</v>
+        <v>741</v>
       </c>
       <c r="D18" t="s">
-        <v>734</v>
+        <v>742</v>
       </c>
       <c r="E18" t="s">
-        <v>735</v>
+        <v>743</v>
       </c>
       <c r="F18" t="s">
-        <v>736</v>
+        <v>744</v>
       </c>
       <c r="G18" t="s">
-        <v>737</v>
+        <v>745</v>
       </c>
       <c r="H18" t="s">
-        <v>738</v>
+        <v>746</v>
       </c>
       <c r="I18" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="19">
@@ -7650,28 +9204,28 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>739</v>
+        <v>747</v>
       </c>
       <c r="C19" t="s">
-        <v>740</v>
+        <v>748</v>
       </c>
       <c r="D19" t="s">
-        <v>741</v>
+        <v>749</v>
       </c>
       <c r="E19" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="F19" t="s">
-        <v>743</v>
+        <v>751</v>
       </c>
       <c r="G19" t="s">
-        <v>744</v>
+        <v>752</v>
       </c>
       <c r="H19" t="s">
-        <v>745</v>
+        <v>753</v>
       </c>
       <c r="I19" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="20">
@@ -7679,28 +9233,28 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>746</v>
+        <v>754</v>
       </c>
       <c r="C20" t="s">
-        <v>747</v>
+        <v>755</v>
       </c>
       <c r="D20" t="s">
-        <v>748</v>
+        <v>756</v>
       </c>
       <c r="E20" t="s">
-        <v>749</v>
+        <v>757</v>
       </c>
       <c r="F20" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="G20" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="H20" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="I20" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="21">
@@ -7708,28 +9262,28 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="C21" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="D21" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="E21" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="F21" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="G21" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="H21" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="I21" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="22">
@@ -7737,28 +9291,28 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="C22" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="D22" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="E22" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="F22" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="G22" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="H22" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="I22" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="23">
@@ -7766,28 +9320,28 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="C23" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="D23" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="E23" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="F23" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="G23" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="H23" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="I23" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="24">
@@ -7795,28 +9349,28 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="C24" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="D24" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="E24" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="F24" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="G24" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="H24" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="I24" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="25">
@@ -7824,28 +9378,28 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="C25" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="D25" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="E25" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="F25" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="G25" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="H25" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="I25" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="26">
@@ -7853,28 +9407,28 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="C26" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="D26" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="E26" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="F26" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="G26" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="H26" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="I26" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="27">
@@ -7882,28 +9436,28 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="C27" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="D27" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="E27" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="F27" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="G27" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="H27" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="I27" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="28">
@@ -7911,28 +9465,28 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="C28" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="D28" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="E28" t="s">
-        <v>742</v>
+        <v>750</v>
       </c>
       <c r="F28" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="G28" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="H28" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="I28" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="29">
@@ -7940,28 +9494,28 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="C29" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="D29" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="E29" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="F29" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="G29" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="H29" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="I29" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="30">
@@ -7969,28 +9523,28 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
+        <v>822</v>
+      </c>
+      <c r="C30" t="s">
+        <v>823</v>
+      </c>
+      <c r="D30" t="s">
+        <v>824</v>
+      </c>
+      <c r="E30" t="s">
+        <v>825</v>
+      </c>
+      <c r="F30" t="s">
+        <v>826</v>
+      </c>
+      <c r="G30" t="s">
+        <v>827</v>
+      </c>
+      <c r="H30" t="s">
+        <v>828</v>
+      </c>
+      <c r="I30" t="s">
         <v>814</v>
-      </c>
-      <c r="C30" t="s">
-        <v>815</v>
-      </c>
-      <c r="D30" t="s">
-        <v>816</v>
-      </c>
-      <c r="E30" t="s">
-        <v>817</v>
-      </c>
-      <c r="F30" t="s">
-        <v>818</v>
-      </c>
-      <c r="G30" t="s">
-        <v>819</v>
-      </c>
-      <c r="H30" t="s">
-        <v>820</v>
-      </c>
-      <c r="I30" t="s">
-        <v>806</v>
       </c>
     </row>
     <row r="31">
@@ -7998,28 +9552,28 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="C31" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="D31" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="E31" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="F31" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="G31" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="H31" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="I31" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="32">
@@ -8027,28 +9581,28 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="C32" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="D32" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="E32" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="F32" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="G32" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="H32" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="I32" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="33">
@@ -8056,28 +9610,28 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="C33" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="D33" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="E33" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="F33" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="G33" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="H33" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="I33" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="34">
@@ -8085,28 +9639,28 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="C34" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="D34" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="E34" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="F34" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="G34" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="H34" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="I34" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="35">
@@ -8114,28 +9668,28 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>847</v>
+        <v>855</v>
       </c>
       <c r="C35" t="s">
-        <v>848</v>
+        <v>856</v>
       </c>
       <c r="D35" t="s">
-        <v>849</v>
+        <v>857</v>
       </c>
       <c r="E35" t="s">
-        <v>850</v>
+        <v>858</v>
       </c>
       <c r="F35" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="G35" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="H35" t="s">
-        <v>852</v>
+        <v>860</v>
       </c>
       <c r="I35" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="36">
@@ -8143,28 +9697,28 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>853</v>
+        <v>861</v>
       </c>
       <c r="C36" t="s">
-        <v>854</v>
+        <v>862</v>
       </c>
       <c r="D36" t="s">
-        <v>855</v>
+        <v>863</v>
       </c>
       <c r="E36" t="s">
-        <v>856</v>
+        <v>864</v>
       </c>
       <c r="F36" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="G36" t="s">
-        <v>857</v>
+        <v>865</v>
       </c>
       <c r="H36" t="s">
-        <v>858</v>
+        <v>866</v>
       </c>
       <c r="I36" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="37">
@@ -8172,28 +9726,28 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>859</v>
+        <v>867</v>
       </c>
       <c r="C37" t="s">
-        <v>860</v>
+        <v>868</v>
       </c>
       <c r="D37" t="s">
-        <v>861</v>
+        <v>869</v>
       </c>
       <c r="E37" t="s">
-        <v>862</v>
+        <v>870</v>
       </c>
       <c r="F37" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="G37" t="s">
-        <v>863</v>
+        <v>871</v>
       </c>
       <c r="H37" t="s">
-        <v>864</v>
+        <v>872</v>
       </c>
       <c r="I37" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="38">
@@ -8201,28 +9755,28 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>865</v>
+        <v>873</v>
       </c>
       <c r="C38" t="s">
-        <v>866</v>
+        <v>874</v>
       </c>
       <c r="D38" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="E38" t="s">
-        <v>868</v>
+        <v>876</v>
       </c>
       <c r="F38" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
       <c r="G38" t="s">
-        <v>870</v>
+        <v>878</v>
       </c>
       <c r="H38" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="I38" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="39">
@@ -8230,28 +9784,28 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>872</v>
+        <v>880</v>
       </c>
       <c r="C39" t="s">
-        <v>873</v>
+        <v>881</v>
       </c>
       <c r="D39" t="s">
-        <v>874</v>
+        <v>882</v>
       </c>
       <c r="E39" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="F39" t="s">
-        <v>875</v>
+        <v>883</v>
       </c>
       <c r="G39" t="s">
-        <v>876</v>
+        <v>884</v>
       </c>
       <c r="H39" t="s">
-        <v>877</v>
+        <v>885</v>
       </c>
       <c r="I39" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="40">
@@ -8259,28 +9813,28 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>879</v>
+        <v>887</v>
       </c>
       <c r="C40" t="s">
-        <v>880</v>
+        <v>888</v>
       </c>
       <c r="D40" t="s">
-        <v>881</v>
+        <v>889</v>
       </c>
       <c r="E40" t="s">
-        <v>882</v>
+        <v>890</v>
       </c>
       <c r="F40" t="s">
-        <v>883</v>
+        <v>891</v>
       </c>
       <c r="G40" t="s">
-        <v>884</v>
+        <v>892</v>
       </c>
       <c r="H40" t="s">
-        <v>885</v>
+        <v>893</v>
       </c>
       <c r="I40" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="41">
@@ -8288,28 +9842,28 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>886</v>
+        <v>894</v>
       </c>
       <c r="C41" t="s">
-        <v>887</v>
+        <v>895</v>
       </c>
       <c r="D41" t="s">
-        <v>888</v>
+        <v>896</v>
       </c>
       <c r="E41" t="s">
-        <v>889</v>
+        <v>897</v>
       </c>
       <c r="F41" t="s">
-        <v>890</v>
+        <v>898</v>
       </c>
       <c r="G41" t="s">
-        <v>891</v>
+        <v>899</v>
       </c>
       <c r="H41" t="s">
-        <v>892</v>
+        <v>900</v>
       </c>
       <c r="I41" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="42">
@@ -8317,28 +9871,28 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>893</v>
+        <v>901</v>
       </c>
       <c r="C42" t="s">
-        <v>894</v>
+        <v>902</v>
       </c>
       <c r="D42" t="s">
-        <v>895</v>
+        <v>903</v>
       </c>
       <c r="E42" t="s">
-        <v>896</v>
+        <v>904</v>
       </c>
       <c r="F42" t="s">
-        <v>851</v>
+        <v>859</v>
       </c>
       <c r="G42" t="s">
-        <v>897</v>
+        <v>905</v>
       </c>
       <c r="H42" t="s">
-        <v>898</v>
+        <v>906</v>
       </c>
       <c r="I42" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="43">
@@ -8346,28 +9900,28 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>899</v>
+        <v>907</v>
       </c>
       <c r="C43" t="s">
-        <v>900</v>
+        <v>908</v>
       </c>
       <c r="D43" t="s">
-        <v>901</v>
+        <v>909</v>
       </c>
       <c r="E43" t="s">
-        <v>902</v>
+        <v>910</v>
       </c>
       <c r="F43" t="s">
-        <v>903</v>
+        <v>911</v>
       </c>
       <c r="G43" t="s">
-        <v>904</v>
+        <v>912</v>
       </c>
       <c r="H43" t="s">
-        <v>905</v>
+        <v>913</v>
       </c>
       <c r="I43" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="44">
@@ -8375,28 +9929,28 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>906</v>
+        <v>914</v>
       </c>
       <c r="C44" t="s">
-        <v>907</v>
+        <v>915</v>
       </c>
       <c r="D44" t="s">
-        <v>908</v>
+        <v>916</v>
       </c>
       <c r="E44" t="s">
-        <v>909</v>
+        <v>917</v>
       </c>
       <c r="F44" t="s">
-        <v>910</v>
+        <v>918</v>
       </c>
       <c r="G44" t="s">
-        <v>911</v>
+        <v>919</v>
       </c>
       <c r="H44" t="s">
-        <v>912</v>
+        <v>920</v>
       </c>
       <c r="I44" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="45">
@@ -8404,28 +9958,28 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>913</v>
+        <v>921</v>
       </c>
       <c r="C45" t="s">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="D45" t="s">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="E45" t="s">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="F45" t="s">
-        <v>917</v>
+        <v>925</v>
       </c>
       <c r="G45" t="s">
-        <v>918</v>
+        <v>926</v>
       </c>
       <c r="H45" t="s">
-        <v>919</v>
+        <v>927</v>
       </c>
       <c r="I45" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="46">
@@ -8433,28 +9987,28 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>920</v>
+        <v>928</v>
       </c>
       <c r="C46" t="s">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="D46" t="s">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="E46" t="s">
-        <v>923</v>
+        <v>931</v>
       </c>
       <c r="F46" t="s">
-        <v>924</v>
+        <v>932</v>
       </c>
       <c r="G46" t="s">
-        <v>925</v>
+        <v>933</v>
       </c>
       <c r="H46" t="s">
-        <v>926</v>
+        <v>934</v>
       </c>
       <c r="I46" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="47">
@@ -8462,28 +10016,28 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>927</v>
+        <v>935</v>
       </c>
       <c r="C47" t="s">
-        <v>928</v>
+        <v>936</v>
       </c>
       <c r="D47" t="s">
-        <v>929</v>
+        <v>937</v>
       </c>
       <c r="E47" t="s">
-        <v>930</v>
+        <v>938</v>
       </c>
       <c r="F47" t="s">
-        <v>931</v>
+        <v>939</v>
       </c>
       <c r="G47" t="s">
-        <v>932</v>
+        <v>940</v>
       </c>
       <c r="H47" t="s">
-        <v>933</v>
+        <v>941</v>
       </c>
       <c r="I47" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="48">
@@ -8491,28 +10045,28 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>934</v>
+        <v>942</v>
       </c>
       <c r="C48" t="s">
-        <v>935</v>
+        <v>943</v>
       </c>
       <c r="D48" t="s">
-        <v>936</v>
+        <v>944</v>
       </c>
       <c r="E48" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="F48" t="s">
-        <v>937</v>
+        <v>945</v>
       </c>
       <c r="G48" t="s">
-        <v>938</v>
+        <v>946</v>
       </c>
       <c r="H48" t="s">
-        <v>939</v>
+        <v>947</v>
       </c>
       <c r="I48" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="49">
@@ -8520,28 +10074,28 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>940</v>
+        <v>948</v>
       </c>
       <c r="C49" t="s">
-        <v>941</v>
+        <v>949</v>
       </c>
       <c r="D49" t="s">
-        <v>942</v>
+        <v>950</v>
       </c>
       <c r="E49" t="s">
-        <v>943</v>
+        <v>951</v>
       </c>
       <c r="F49" t="s">
-        <v>944</v>
+        <v>952</v>
       </c>
       <c r="G49" t="s">
-        <v>945</v>
+        <v>953</v>
       </c>
       <c r="H49" t="s">
-        <v>946</v>
+        <v>954</v>
       </c>
       <c r="I49" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="50">
@@ -8549,28 +10103,28 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>947</v>
+        <v>955</v>
       </c>
       <c r="C50" t="s">
-        <v>948</v>
+        <v>956</v>
       </c>
       <c r="D50" t="s">
-        <v>949</v>
+        <v>957</v>
       </c>
       <c r="E50" t="s">
-        <v>950</v>
+        <v>958</v>
       </c>
       <c r="F50" t="s">
-        <v>951</v>
+        <v>959</v>
       </c>
       <c r="G50" t="s">
-        <v>952</v>
+        <v>960</v>
       </c>
       <c r="H50" t="s">
-        <v>953</v>
+        <v>961</v>
       </c>
       <c r="I50" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="51">
@@ -8578,28 +10132,28 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>954</v>
+        <v>962</v>
       </c>
       <c r="C51" t="s">
-        <v>955</v>
+        <v>963</v>
       </c>
       <c r="D51" t="s">
-        <v>956</v>
+        <v>964</v>
       </c>
       <c r="E51" t="s">
-        <v>957</v>
+        <v>965</v>
       </c>
       <c r="F51" t="s">
-        <v>958</v>
+        <v>966</v>
       </c>
       <c r="G51" t="s">
-        <v>959</v>
+        <v>967</v>
       </c>
       <c r="H51" t="s">
-        <v>960</v>
+        <v>968</v>
       </c>
       <c r="I51" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="52">
@@ -8607,28 +10161,28 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>961</v>
+        <v>969</v>
       </c>
       <c r="C52" t="s">
-        <v>962</v>
+        <v>970</v>
       </c>
       <c r="D52" t="s">
-        <v>963</v>
+        <v>971</v>
       </c>
       <c r="E52" t="s">
-        <v>964</v>
+        <v>972</v>
       </c>
       <c r="F52" t="s">
-        <v>965</v>
+        <v>973</v>
       </c>
       <c r="G52" t="s">
-        <v>966</v>
+        <v>974</v>
       </c>
       <c r="H52" t="s">
-        <v>967</v>
+        <v>975</v>
       </c>
       <c r="I52" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="53">
@@ -8636,28 +10190,28 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>968</v>
+        <v>976</v>
       </c>
       <c r="C53" t="s">
-        <v>969</v>
+        <v>977</v>
       </c>
       <c r="D53" t="s">
-        <v>970</v>
+        <v>978</v>
       </c>
       <c r="E53" t="s">
-        <v>971</v>
+        <v>979</v>
       </c>
       <c r="F53" t="s">
-        <v>972</v>
+        <v>980</v>
       </c>
       <c r="G53" t="s">
-        <v>973</v>
+        <v>981</v>
       </c>
       <c r="H53" t="s">
-        <v>974</v>
+        <v>982</v>
       </c>
       <c r="I53" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="54">
@@ -8665,28 +10219,28 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>975</v>
+        <v>983</v>
       </c>
       <c r="C54" t="s">
-        <v>976</v>
+        <v>984</v>
       </c>
       <c r="D54" t="s">
-        <v>977</v>
+        <v>985</v>
       </c>
       <c r="E54" t="s">
-        <v>978</v>
+        <v>986</v>
       </c>
       <c r="F54" t="s">
-        <v>979</v>
+        <v>987</v>
       </c>
       <c r="G54" t="s">
-        <v>980</v>
+        <v>988</v>
       </c>
       <c r="H54" t="s">
-        <v>981</v>
+        <v>989</v>
       </c>
       <c r="I54" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
     </row>
     <row r="55">
@@ -8694,28 +10248,28 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>982</v>
+        <v>990</v>
       </c>
       <c r="C55" t="s">
-        <v>983</v>
+        <v>991</v>
       </c>
       <c r="D55" t="s">
-        <v>984</v>
+        <v>992</v>
       </c>
       <c r="E55" t="s">
-        <v>985</v>
+        <v>993</v>
       </c>
       <c r="F55" t="s">
-        <v>986</v>
+        <v>994</v>
       </c>
       <c r="G55" t="s">
-        <v>987</v>
+        <v>995</v>
       </c>
       <c r="H55" t="s">
-        <v>988</v>
+        <v>996</v>
       </c>
       <c r="I55" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="56">
@@ -8723,28 +10277,28 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>989</v>
+        <v>997</v>
       </c>
       <c r="C56" t="s">
-        <v>990</v>
+        <v>998</v>
       </c>
       <c r="D56" t="s">
-        <v>991</v>
+        <v>999</v>
       </c>
       <c r="E56" t="s">
-        <v>992</v>
+        <v>1000</v>
       </c>
       <c r="F56" t="s">
-        <v>993</v>
+        <v>1001</v>
       </c>
       <c r="G56" t="s">
-        <v>994</v>
+        <v>1002</v>
       </c>
       <c r="H56" t="s">
-        <v>995</v>
+        <v>1003</v>
       </c>
       <c r="I56" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="57">
@@ -8752,28 +10306,28 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>996</v>
+        <v>1004</v>
       </c>
       <c r="C57" t="s">
-        <v>997</v>
+        <v>1005</v>
       </c>
       <c r="D57" t="s">
-        <v>998</v>
+        <v>1006</v>
       </c>
       <c r="E57" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="F57" t="s">
-        <v>1000</v>
+        <v>1008</v>
       </c>
       <c r="G57" t="s">
-        <v>1001</v>
+        <v>1009</v>
       </c>
       <c r="H57" t="s">
-        <v>1002</v>
+        <v>1010</v>
       </c>
       <c r="I57" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="58">
@@ -8781,28 +10335,28 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>1003</v>
+        <v>1011</v>
       </c>
       <c r="C58" t="s">
-        <v>1004</v>
+        <v>1012</v>
       </c>
       <c r="D58" t="s">
-        <v>1005</v>
+        <v>1013</v>
       </c>
       <c r="E58" t="s">
-        <v>999</v>
+        <v>1007</v>
       </c>
       <c r="F58" t="s">
-        <v>1006</v>
+        <v>1014</v>
       </c>
       <c r="G58" t="s">
-        <v>1007</v>
+        <v>1015</v>
       </c>
       <c r="H58" t="s">
-        <v>1008</v>
+        <v>1016</v>
       </c>
       <c r="I58" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="59">
@@ -8810,28 +10364,28 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>1009</v>
+        <v>1017</v>
       </c>
       <c r="C59" t="s">
-        <v>1010</v>
+        <v>1018</v>
       </c>
       <c r="D59" t="s">
-        <v>1011</v>
+        <v>1019</v>
       </c>
       <c r="E59" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="F59" t="s">
-        <v>1013</v>
+        <v>1021</v>
       </c>
       <c r="G59" t="s">
-        <v>1014</v>
+        <v>1022</v>
       </c>
       <c r="H59" t="s">
-        <v>1015</v>
+        <v>1023</v>
       </c>
       <c r="I59" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="60">
@@ -8839,28 +10393,28 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>1016</v>
+        <v>1024</v>
       </c>
       <c r="C60" t="s">
-        <v>1017</v>
+        <v>1025</v>
       </c>
       <c r="D60" t="s">
-        <v>1018</v>
+        <v>1026</v>
       </c>
       <c r="E60" t="s">
-        <v>1019</v>
+        <v>1027</v>
       </c>
       <c r="F60" t="s">
-        <v>1020</v>
+        <v>1028</v>
       </c>
       <c r="G60" t="s">
-        <v>1021</v>
+        <v>1029</v>
       </c>
       <c r="H60" t="s">
-        <v>1022</v>
+        <v>1030</v>
       </c>
       <c r="I60" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="61">
@@ -8868,28 +10422,28 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>1023</v>
+        <v>1031</v>
       </c>
       <c r="C61" t="s">
-        <v>1024</v>
+        <v>1032</v>
       </c>
       <c r="D61" t="s">
-        <v>1025</v>
+        <v>1033</v>
       </c>
       <c r="E61" t="s">
-        <v>1026</v>
+        <v>1034</v>
       </c>
       <c r="F61" t="s">
-        <v>1027</v>
+        <v>1035</v>
       </c>
       <c r="G61" t="s">
-        <v>1028</v>
+        <v>1036</v>
       </c>
       <c r="H61" t="s">
-        <v>1029</v>
+        <v>1037</v>
       </c>
       <c r="I61" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="62">
@@ -8897,28 +10451,28 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>1030</v>
+        <v>1038</v>
       </c>
       <c r="C62" t="s">
-        <v>1031</v>
+        <v>1039</v>
       </c>
       <c r="D62" t="s">
-        <v>1032</v>
+        <v>1040</v>
       </c>
       <c r="E62" t="s">
-        <v>1033</v>
+        <v>1041</v>
       </c>
       <c r="F62" t="s">
-        <v>1034</v>
+        <v>1042</v>
       </c>
       <c r="G62" t="s">
-        <v>1035</v>
+        <v>1043</v>
       </c>
       <c r="H62" t="s">
-        <v>1036</v>
+        <v>1044</v>
       </c>
       <c r="I62" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="63">
@@ -8926,28 +10480,28 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>1037</v>
+        <v>1045</v>
       </c>
       <c r="C63" t="s">
-        <v>1038</v>
+        <v>1046</v>
       </c>
       <c r="D63" t="s">
-        <v>1039</v>
+        <v>1047</v>
       </c>
       <c r="E63" t="s">
-        <v>1040</v>
+        <v>1048</v>
       </c>
       <c r="F63" t="s">
-        <v>1041</v>
+        <v>1049</v>
       </c>
       <c r="G63" t="s">
-        <v>1042</v>
+        <v>1050</v>
       </c>
       <c r="H63" t="s">
-        <v>1043</v>
+        <v>1051</v>
       </c>
       <c r="I63" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="64">
@@ -8955,28 +10509,28 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>1044</v>
+        <v>1052</v>
       </c>
       <c r="C64" t="s">
-        <v>1045</v>
+        <v>1053</v>
       </c>
       <c r="D64" t="s">
-        <v>1046</v>
+        <v>1054</v>
       </c>
       <c r="E64" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="F64" t="s">
-        <v>1047</v>
+        <v>1055</v>
       </c>
       <c r="G64" t="s">
-        <v>1048</v>
+        <v>1056</v>
       </c>
       <c r="H64" t="s">
-        <v>1049</v>
+        <v>1057</v>
       </c>
       <c r="I64" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="65">
@@ -8984,28 +10538,28 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>1050</v>
+        <v>1058</v>
       </c>
       <c r="C65" t="s">
-        <v>1051</v>
+        <v>1059</v>
       </c>
       <c r="D65" t="s">
-        <v>1052</v>
+        <v>1060</v>
       </c>
       <c r="E65" t="s">
-        <v>1053</v>
+        <v>1061</v>
       </c>
       <c r="F65" t="s">
-        <v>1054</v>
+        <v>1062</v>
       </c>
       <c r="G65" t="s">
-        <v>1055</v>
+        <v>1063</v>
       </c>
       <c r="H65" t="s">
-        <v>1056</v>
+        <v>1064</v>
       </c>
       <c r="I65" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="66">
@@ -9013,28 +10567,28 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>1057</v>
+        <v>1065</v>
       </c>
       <c r="C66" t="s">
-        <v>1058</v>
+        <v>1066</v>
       </c>
       <c r="D66" t="s">
-        <v>1059</v>
+        <v>1067</v>
       </c>
       <c r="E66" t="s">
-        <v>1060</v>
+        <v>1068</v>
       </c>
       <c r="F66" t="s">
-        <v>1061</v>
+        <v>1069</v>
       </c>
       <c r="G66" t="s">
-        <v>1062</v>
+        <v>1070</v>
       </c>
       <c r="H66" t="s">
-        <v>1063</v>
+        <v>1071</v>
       </c>
       <c r="I66" t="s">
-        <v>623</v>
+        <v>631</v>
       </c>
     </row>
     <row r="67">
@@ -9042,28 +10596,28 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>1064</v>
+        <v>1072</v>
       </c>
       <c r="C67" t="s">
-        <v>1065</v>
+        <v>1073</v>
       </c>
       <c r="D67" t="s">
-        <v>1066</v>
+        <v>1074</v>
       </c>
       <c r="E67" t="s">
-        <v>1067</v>
+        <v>1075</v>
       </c>
       <c r="F67" t="s">
-        <v>1068</v>
+        <v>1076</v>
       </c>
       <c r="G67" t="s">
-        <v>1069</v>
+        <v>1077</v>
       </c>
       <c r="H67" t="s">
-        <v>1070</v>
+        <v>1078</v>
       </c>
       <c r="I67" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="68">
@@ -9071,28 +10625,28 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>1071</v>
+        <v>1079</v>
       </c>
       <c r="C68" t="s">
-        <v>1072</v>
+        <v>1080</v>
       </c>
       <c r="D68" t="s">
-        <v>1073</v>
+        <v>1081</v>
       </c>
       <c r="E68" t="s">
-        <v>1012</v>
+        <v>1020</v>
       </c>
       <c r="F68" t="s">
-        <v>1074</v>
+        <v>1082</v>
       </c>
       <c r="G68" t="s">
-        <v>1075</v>
+        <v>1083</v>
       </c>
       <c r="H68" t="s">
-        <v>1076</v>
+        <v>1084</v>
       </c>
       <c r="I68" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="69">
@@ -9100,28 +10654,28 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>1077</v>
+        <v>1085</v>
       </c>
       <c r="C69" t="s">
-        <v>1078</v>
+        <v>1086</v>
       </c>
       <c r="D69" t="s">
-        <v>1079</v>
+        <v>1087</v>
       </c>
       <c r="E69" t="s">
-        <v>1080</v>
+        <v>1088</v>
       </c>
       <c r="F69" t="s">
-        <v>1081</v>
+        <v>1089</v>
       </c>
       <c r="G69" t="s">
-        <v>1082</v>
+        <v>1090</v>
       </c>
       <c r="H69" t="s">
-        <v>1083</v>
+        <v>1091</v>
       </c>
       <c r="I69" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="70">
@@ -9129,28 +10683,28 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>1084</v>
+        <v>1092</v>
       </c>
       <c r="C70" t="s">
-        <v>1085</v>
+        <v>1093</v>
       </c>
       <c r="D70" t="s">
-        <v>1086</v>
+        <v>1094</v>
       </c>
       <c r="E70" t="s">
-        <v>1087</v>
+        <v>1095</v>
       </c>
       <c r="F70" t="s">
-        <v>1088</v>
+        <v>1096</v>
       </c>
       <c r="G70" t="s">
-        <v>1089</v>
+        <v>1097</v>
       </c>
       <c r="H70" t="s">
-        <v>1090</v>
+        <v>1098</v>
       </c>
       <c r="I70" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="71">
@@ -9158,28 +10712,28 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>1091</v>
+        <v>1099</v>
       </c>
       <c r="C71" t="s">
-        <v>1092</v>
+        <v>1100</v>
       </c>
       <c r="D71" t="s">
-        <v>1093</v>
+        <v>1101</v>
       </c>
       <c r="E71" t="s">
-        <v>1094</v>
+        <v>1102</v>
       </c>
       <c r="F71" t="s">
-        <v>1095</v>
+        <v>1103</v>
       </c>
       <c r="G71" t="s">
-        <v>1096</v>
+        <v>1104</v>
       </c>
       <c r="H71" t="s">
-        <v>1097</v>
+        <v>1105</v>
       </c>
       <c r="I71" t="s">
-        <v>878</v>
+        <v>886</v>
       </c>
     </row>
     <row r="72">
@@ -9187,28 +10741,28 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>1098</v>
+        <v>1106</v>
       </c>
       <c r="C72" t="s">
-        <v>1099</v>
+        <v>1107</v>
       </c>
       <c r="D72" t="s">
-        <v>1100</v>
+        <v>1108</v>
       </c>
       <c r="E72" t="s">
-        <v>1101</v>
+        <v>1109</v>
       </c>
       <c r="F72" t="s">
-        <v>1102</v>
+        <v>1110</v>
       </c>
       <c r="G72" t="s">
-        <v>1103</v>
+        <v>1111</v>
       </c>
       <c r="H72" t="s">
-        <v>1104</v>
+        <v>1112</v>
       </c>
       <c r="I72" t="s">
-        <v>1105</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="73">
@@ -9216,28 +10770,28 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>1106</v>
+        <v>1114</v>
       </c>
       <c r="C73" t="s">
-        <v>1107</v>
+        <v>1115</v>
       </c>
       <c r="D73" t="s">
-        <v>1108</v>
+        <v>1116</v>
       </c>
       <c r="E73" t="s">
-        <v>1109</v>
+        <v>1117</v>
       </c>
       <c r="F73" t="s">
-        <v>1110</v>
+        <v>1118</v>
       </c>
       <c r="G73" t="s">
-        <v>1111</v>
+        <v>1119</v>
       </c>
       <c r="H73" t="s">
-        <v>1112</v>
+        <v>1120</v>
       </c>
       <c r="I73" t="s">
-        <v>1113</v>
+        <v>1121</v>
       </c>
     </row>
     <row r="74">
@@ -9245,28 +10799,28 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>1114</v>
+        <v>1122</v>
       </c>
       <c r="C74" t="s">
-        <v>1115</v>
+        <v>1123</v>
       </c>
       <c r="D74" t="s">
-        <v>1116</v>
+        <v>1124</v>
       </c>
       <c r="E74" t="s">
-        <v>1117</v>
+        <v>1125</v>
       </c>
       <c r="F74" t="s">
-        <v>1118</v>
+        <v>1126</v>
       </c>
       <c r="G74" t="s">
-        <v>1119</v>
+        <v>1127</v>
       </c>
       <c r="H74" t="s">
-        <v>1120</v>
+        <v>1128</v>
       </c>
       <c r="I74" t="s">
-        <v>1121</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="75">
@@ -9274,28 +10828,28 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>1122</v>
+        <v>1130</v>
       </c>
       <c r="C75" t="s">
-        <v>1123</v>
+        <v>1131</v>
       </c>
       <c r="D75" t="s">
-        <v>1124</v>
+        <v>1132</v>
       </c>
       <c r="E75" t="s">
-        <v>1125</v>
+        <v>1133</v>
       </c>
       <c r="F75" t="s">
-        <v>1126</v>
+        <v>1134</v>
       </c>
       <c r="G75" t="s">
-        <v>1127</v>
+        <v>1135</v>
       </c>
       <c r="H75" t="s">
-        <v>1128</v>
+        <v>1136</v>
       </c>
       <c r="I75" t="s">
-        <v>1129</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="76">
@@ -9303,42 +10857,58 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>1130</v>
+        <v>1138</v>
       </c>
       <c r="C76" t="s">
-        <v>1131</v>
+        <v>1139</v>
       </c>
       <c r="D76" t="s">
-        <v>1132</v>
+        <v>1140</v>
       </c>
       <c r="E76" t="s">
-        <v>1133</v>
+        <v>1141</v>
       </c>
       <c r="F76" t="s">
-        <v>1134</v>
+        <v>1142</v>
       </c>
       <c r="G76" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="H76" t="s">
-        <v>1136</v>
+        <v>1144</v>
       </c>
       <c r="I76" t="s">
-        <v>1137</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
         <v>75</v>
       </c>
-      <c r="B77"/>
-      <c r="C77"/>
-      <c r="D77"/>
-      <c r="E77"/>
-      <c r="F77"/>
-      <c r="G77"/>
-      <c r="H77"/>
-      <c r="I77"/>
+      <c r="B77" t="s">
+        <v>1146</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1147</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1148</v>
+      </c>
+      <c r="E77" t="s">
+        <v>1149</v>
+      </c>
+      <c r="F77" t="s">
+        <v>1150</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1152</v>
+      </c>
+      <c r="I77" t="s">
+        <v>1153</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9356,28 +10926,28 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1138</v>
+        <v>1154</v>
       </c>
       <c r="C1" t="s">
-        <v>1139</v>
+        <v>1155</v>
       </c>
       <c r="D1" t="s">
-        <v>610</v>
+        <v>618</v>
       </c>
       <c r="E1" t="s">
-        <v>611</v>
+        <v>619</v>
       </c>
       <c r="F1" t="s">
-        <v>1140</v>
+        <v>1156</v>
       </c>
       <c r="G1" t="s">
-        <v>1141</v>
+        <v>1157</v>
       </c>
       <c r="H1" t="s">
-        <v>614</v>
+        <v>622</v>
       </c>
       <c r="I1" t="s">
-        <v>615</v>
+        <v>623</v>
       </c>
     </row>
     <row r="2">
@@ -9385,13 +10955,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>1142</v>
+        <v>1158</v>
       </c>
       <c r="C2" t="s">
-        <v>1143</v>
+        <v>1159</v>
       </c>
       <c r="D2" t="s">
-        <v>1144</v>
+        <v>1160</v>
       </c>
       <c r="E2" t="s">
         <v>21</v>
@@ -9406,13 +10976,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>1145</v>
+        <v>1161</v>
       </c>
       <c r="C3" t="s">
-        <v>1146</v>
+        <v>1162</v>
       </c>
       <c r="D3" t="s">
-        <v>1147</v>
+        <v>1163</v>
       </c>
       <c r="E3" t="s">
         <v>21</v>
@@ -9427,13 +10997,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>1148</v>
+        <v>1164</v>
       </c>
       <c r="C4" t="s">
-        <v>1149</v>
+        <v>1165</v>
       </c>
       <c r="D4" t="s">
-        <v>1150</v>
+        <v>1166</v>
       </c>
       <c r="E4" t="s">
         <v>21</v>
@@ -9448,13 +11018,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>1151</v>
+        <v>1167</v>
       </c>
       <c r="C5" t="s">
-        <v>1152</v>
+        <v>1168</v>
       </c>
       <c r="D5" t="s">
-        <v>1153</v>
+        <v>1169</v>
       </c>
       <c r="E5" t="s">
         <v>21</v>
@@ -9469,13 +11039,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>1154</v>
+        <v>1170</v>
       </c>
       <c r="C6" t="s">
-        <v>1155</v>
+        <v>1171</v>
       </c>
       <c r="D6" t="s">
-        <v>1156</v>
+        <v>1172</v>
       </c>
       <c r="E6" t="s">
         <v>21</v>
@@ -9490,13 +11060,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>1157</v>
+        <v>1173</v>
       </c>
       <c r="C7" t="s">
-        <v>1158</v>
+        <v>1174</v>
       </c>
       <c r="D7" t="s">
-        <v>1159</v>
+        <v>1175</v>
       </c>
       <c r="E7" t="s">
         <v>21</v>
@@ -9511,13 +11081,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>1160</v>
+        <v>1176</v>
       </c>
       <c r="C8" t="s">
-        <v>1161</v>
+        <v>1177</v>
       </c>
       <c r="D8" t="s">
-        <v>1162</v>
+        <v>1178</v>
       </c>
       <c r="E8" t="s">
         <v>21</v>
@@ -9532,13 +11102,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>1163</v>
+        <v>1179</v>
       </c>
       <c r="C9" t="s">
-        <v>1164</v>
+        <v>1180</v>
       </c>
       <c r="D9" t="s">
-        <v>1165</v>
+        <v>1181</v>
       </c>
       <c r="E9" t="s">
         <v>21</v>
@@ -9553,13 +11123,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>1166</v>
+        <v>1182</v>
       </c>
       <c r="C10" t="s">
-        <v>1167</v>
+        <v>1183</v>
       </c>
       <c r="D10" t="s">
-        <v>1168</v>
+        <v>1184</v>
       </c>
       <c r="E10" t="s">
         <v>21</v>
@@ -9574,13 +11144,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>1169</v>
+        <v>1185</v>
       </c>
       <c r="C11" t="s">
-        <v>1170</v>
+        <v>1186</v>
       </c>
       <c r="D11" t="s">
-        <v>1171</v>
+        <v>1187</v>
       </c>
       <c r="E11" t="s">
         <v>21</v>
@@ -9595,13 +11165,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>1172</v>
+        <v>1188</v>
       </c>
       <c r="C12" t="s">
-        <v>1173</v>
+        <v>1189</v>
       </c>
       <c r="D12" t="s">
-        <v>1174</v>
+        <v>1190</v>
       </c>
       <c r="E12" t="s">
         <v>21</v>
@@ -9616,13 +11186,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>1175</v>
+        <v>1191</v>
       </c>
       <c r="C13" t="s">
-        <v>1176</v>
+        <v>1192</v>
       </c>
       <c r="D13" t="s">
-        <v>1177</v>
+        <v>1193</v>
       </c>
       <c r="E13" t="s">
         <v>21</v>
@@ -9637,13 +11207,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>1178</v>
+        <v>1194</v>
       </c>
       <c r="C14" t="s">
-        <v>1179</v>
+        <v>1195</v>
       </c>
       <c r="D14" t="s">
-        <v>1180</v>
+        <v>1196</v>
       </c>
       <c r="E14" t="s">
         <v>21</v>
@@ -9658,13 +11228,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>1181</v>
+        <v>1197</v>
       </c>
       <c r="C15" t="s">
-        <v>1182</v>
+        <v>1198</v>
       </c>
       <c r="D15" t="s">
-        <v>1183</v>
+        <v>1199</v>
       </c>
       <c r="E15" t="s">
         <v>21</v>
@@ -9679,13 +11249,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>1184</v>
+        <v>1200</v>
       </c>
       <c r="C16" t="s">
-        <v>1185</v>
+        <v>1201</v>
       </c>
       <c r="D16" t="s">
-        <v>1186</v>
+        <v>1202</v>
       </c>
       <c r="E16" t="s">
         <v>21</v>
@@ -9700,13 +11270,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>1187</v>
+        <v>1203</v>
       </c>
       <c r="C17" t="s">
-        <v>1188</v>
+        <v>1204</v>
       </c>
       <c r="D17" t="s">
-        <v>1189</v>
+        <v>1205</v>
       </c>
       <c r="E17" t="s">
         <v>21</v>
@@ -9721,13 +11291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="C18" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="D18" t="s">
-        <v>1192</v>
+        <v>1208</v>
       </c>
       <c r="E18" t="s">
         <v>21</v>
@@ -9742,13 +11312,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>1193</v>
+        <v>1209</v>
       </c>
       <c r="C19" t="s">
-        <v>1194</v>
+        <v>1210</v>
       </c>
       <c r="D19" t="s">
-        <v>1195</v>
+        <v>1211</v>
       </c>
       <c r="E19" t="s">
         <v>21</v>
@@ -9763,13 +11333,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>1196</v>
+        <v>1212</v>
       </c>
       <c r="C20" t="s">
-        <v>1197</v>
+        <v>1213</v>
       </c>
       <c r="D20" t="s">
-        <v>1198</v>
+        <v>1214</v>
       </c>
       <c r="E20" t="s">
         <v>21</v>
@@ -9784,13 +11354,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>1199</v>
+        <v>1215</v>
       </c>
       <c r="C21" t="s">
-        <v>1200</v>
+        <v>1216</v>
       </c>
       <c r="D21" t="s">
-        <v>1201</v>
+        <v>1217</v>
       </c>
       <c r="E21" t="s">
         <v>21</v>
@@ -9805,13 +11375,13 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>1202</v>
+        <v>1218</v>
       </c>
       <c r="C22" t="s">
-        <v>1203</v>
+        <v>1219</v>
       </c>
       <c r="D22" t="s">
-        <v>1204</v>
+        <v>1220</v>
       </c>
       <c r="E22" t="s">
         <v>21</v>
@@ -9826,13 +11396,13 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>1205</v>
+        <v>1221</v>
       </c>
       <c r="C23" t="s">
-        <v>1206</v>
+        <v>1222</v>
       </c>
       <c r="D23" t="s">
-        <v>1207</v>
+        <v>1223</v>
       </c>
       <c r="E23" t="s">
         <v>21</v>
@@ -9847,13 +11417,13 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>1208</v>
+        <v>1224</v>
       </c>
       <c r="C24" t="s">
-        <v>1209</v>
+        <v>1225</v>
       </c>
       <c r="D24" t="s">
-        <v>1210</v>
+        <v>1226</v>
       </c>
       <c r="E24" t="s">
         <v>21</v>
@@ -9868,13 +11438,13 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>1211</v>
+        <v>1227</v>
       </c>
       <c r="C25" t="s">
-        <v>1212</v>
+        <v>1228</v>
       </c>
       <c r="D25" t="s">
-        <v>1213</v>
+        <v>1229</v>
       </c>
       <c r="E25" t="s">
         <v>21</v>
@@ -9889,13 +11459,13 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>1214</v>
+        <v>1230</v>
       </c>
       <c r="C26" t="s">
-        <v>1215</v>
+        <v>1231</v>
       </c>
       <c r="D26" t="s">
-        <v>1216</v>
+        <v>1232</v>
       </c>
       <c r="E26" t="s">
         <v>21</v>
@@ -9910,13 +11480,13 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>1217</v>
+        <v>1233</v>
       </c>
       <c r="C27" t="s">
-        <v>1218</v>
+        <v>1234</v>
       </c>
       <c r="D27" t="s">
-        <v>1219</v>
+        <v>1235</v>
       </c>
       <c r="E27" t="s">
         <v>21</v>
@@ -9931,13 +11501,13 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>1220</v>
+        <v>1236</v>
       </c>
       <c r="C28" t="s">
-        <v>1221</v>
+        <v>1237</v>
       </c>
       <c r="D28" t="s">
-        <v>1222</v>
+        <v>1238</v>
       </c>
       <c r="E28" t="s">
         <v>21</v>
@@ -9952,13 +11522,13 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>1223</v>
+        <v>1239</v>
       </c>
       <c r="C29" t="s">
-        <v>1224</v>
+        <v>1240</v>
       </c>
       <c r="D29" t="s">
-        <v>1225</v>
+        <v>1241</v>
       </c>
       <c r="E29" t="s">
         <v>21</v>
@@ -9973,13 +11543,13 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>1226</v>
+        <v>1242</v>
       </c>
       <c r="C30" t="s">
-        <v>1227</v>
+        <v>1243</v>
       </c>
       <c r="D30" t="s">
-        <v>1228</v>
+        <v>1244</v>
       </c>
       <c r="E30" t="s">
         <v>21</v>
@@ -9994,13 +11564,13 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>1229</v>
+        <v>1245</v>
       </c>
       <c r="C31" t="s">
-        <v>1230</v>
+        <v>1246</v>
       </c>
       <c r="D31" t="s">
-        <v>1231</v>
+        <v>1247</v>
       </c>
       <c r="E31" t="s">
         <v>21</v>
@@ -10015,13 +11585,13 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>1232</v>
+        <v>1248</v>
       </c>
       <c r="C32" t="s">
-        <v>1233</v>
+        <v>1249</v>
       </c>
       <c r="D32" t="s">
-        <v>1234</v>
+        <v>1250</v>
       </c>
       <c r="E32" t="s">
         <v>21</v>
@@ -10036,13 +11606,13 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>1235</v>
+        <v>1251</v>
       </c>
       <c r="C33" t="s">
-        <v>1236</v>
+        <v>1252</v>
       </c>
       <c r="D33" t="s">
-        <v>1237</v>
+        <v>1253</v>
       </c>
       <c r="E33" t="s">
         <v>21</v>
@@ -10057,13 +11627,13 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>1238</v>
+        <v>1254</v>
       </c>
       <c r="C34" t="s">
-        <v>1239</v>
+        <v>1255</v>
       </c>
       <c r="D34" t="s">
-        <v>1240</v>
+        <v>1256</v>
       </c>
       <c r="E34" t="s">
         <v>21</v>
@@ -10078,13 +11648,13 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>1241</v>
+        <v>1257</v>
       </c>
       <c r="C35" t="s">
-        <v>1242</v>
+        <v>1258</v>
       </c>
       <c r="D35" t="s">
-        <v>1243</v>
+        <v>1259</v>
       </c>
       <c r="E35" t="s">
         <v>21</v>
@@ -10099,13 +11669,13 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>1244</v>
+        <v>1260</v>
       </c>
       <c r="C36" t="s">
-        <v>1245</v>
+        <v>1261</v>
       </c>
       <c r="D36" t="s">
-        <v>1246</v>
+        <v>1262</v>
       </c>
       <c r="E36" t="s">
         <v>21</v>
@@ -10120,13 +11690,13 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>1247</v>
+        <v>1263</v>
       </c>
       <c r="C37" t="s">
-        <v>1248</v>
+        <v>1264</v>
       </c>
       <c r="D37" t="s">
-        <v>1249</v>
+        <v>1265</v>
       </c>
       <c r="E37" t="s">
         <v>21</v>
@@ -10141,13 +11711,13 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>1250</v>
+        <v>1266</v>
       </c>
       <c r="C38" t="s">
-        <v>1251</v>
+        <v>1267</v>
       </c>
       <c r="D38" t="s">
-        <v>1252</v>
+        <v>1268</v>
       </c>
       <c r="E38" t="s">
         <v>21</v>
@@ -10162,13 +11732,13 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>1253</v>
+        <v>1269</v>
       </c>
       <c r="C39" t="s">
-        <v>1254</v>
+        <v>1270</v>
       </c>
       <c r="D39" t="s">
-        <v>1255</v>
+        <v>1271</v>
       </c>
       <c r="E39" t="s">
         <v>21</v>
@@ -10183,13 +11753,13 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>1256</v>
+        <v>1272</v>
       </c>
       <c r="C40" t="s">
-        <v>1257</v>
+        <v>1273</v>
       </c>
       <c r="D40" t="s">
-        <v>1258</v>
+        <v>1274</v>
       </c>
       <c r="E40" t="s">
         <v>21</v>
@@ -10204,13 +11774,13 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>1259</v>
+        <v>1275</v>
       </c>
       <c r="C41" t="s">
-        <v>1260</v>
+        <v>1276</v>
       </c>
       <c r="D41" t="s">
-        <v>1261</v>
+        <v>1277</v>
       </c>
       <c r="E41" t="s">
         <v>21</v>
@@ -10225,13 +11795,13 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>1262</v>
+        <v>1278</v>
       </c>
       <c r="C42" t="s">
-        <v>1263</v>
+        <v>1279</v>
       </c>
       <c r="D42" t="s">
-        <v>1264</v>
+        <v>1280</v>
       </c>
       <c r="E42" t="s">
         <v>21</v>
@@ -10246,13 +11816,13 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>1265</v>
+        <v>1281</v>
       </c>
       <c r="C43" t="s">
-        <v>1266</v>
+        <v>1282</v>
       </c>
       <c r="D43" t="s">
-        <v>1267</v>
+        <v>1283</v>
       </c>
       <c r="E43" t="s">
         <v>21</v>
@@ -10267,13 +11837,13 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>1268</v>
+        <v>1284</v>
       </c>
       <c r="C44" t="s">
-        <v>1269</v>
+        <v>1285</v>
       </c>
       <c r="D44" t="s">
-        <v>1270</v>
+        <v>1286</v>
       </c>
       <c r="E44" t="s">
         <v>21</v>
@@ -10288,13 +11858,13 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>1271</v>
+        <v>1287</v>
       </c>
       <c r="C45" t="s">
-        <v>1272</v>
+        <v>1288</v>
       </c>
       <c r="D45" t="s">
-        <v>1273</v>
+        <v>1289</v>
       </c>
       <c r="E45" t="s">
         <v>21</v>
@@ -10309,13 +11879,13 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>1274</v>
+        <v>1290</v>
       </c>
       <c r="C46" t="s">
-        <v>1275</v>
+        <v>1291</v>
       </c>
       <c r="D46" t="s">
-        <v>1276</v>
+        <v>1292</v>
       </c>
       <c r="E46" t="s">
         <v>21</v>
@@ -10330,13 +11900,13 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>1277</v>
+        <v>1293</v>
       </c>
       <c r="C47" t="s">
-        <v>1278</v>
+        <v>1294</v>
       </c>
       <c r="D47" t="s">
-        <v>1279</v>
+        <v>1295</v>
       </c>
       <c r="E47" t="s">
         <v>21</v>
@@ -10351,13 +11921,13 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>1280</v>
+        <v>1296</v>
       </c>
       <c r="C48" t="s">
-        <v>1281</v>
+        <v>1297</v>
       </c>
       <c r="D48" t="s">
-        <v>1282</v>
+        <v>1298</v>
       </c>
       <c r="E48" t="s">
         <v>21</v>
@@ -10372,13 +11942,13 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>1283</v>
+        <v>1299</v>
       </c>
       <c r="C49" t="s">
-        <v>1284</v>
+        <v>1300</v>
       </c>
       <c r="D49" t="s">
-        <v>1285</v>
+        <v>1301</v>
       </c>
       <c r="E49" t="s">
         <v>21</v>
@@ -10393,13 +11963,13 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>1286</v>
+        <v>1302</v>
       </c>
       <c r="C50" t="s">
-        <v>1287</v>
+        <v>1303</v>
       </c>
       <c r="D50" t="s">
-        <v>1288</v>
+        <v>1304</v>
       </c>
       <c r="E50" t="s">
         <v>21</v>
@@ -10414,13 +11984,13 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>1289</v>
+        <v>1305</v>
       </c>
       <c r="C51" t="s">
-        <v>1290</v>
+        <v>1306</v>
       </c>
       <c r="D51" t="s">
-        <v>1291</v>
+        <v>1307</v>
       </c>
       <c r="E51" t="s">
         <v>21</v>
@@ -10435,13 +12005,13 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>1292</v>
+        <v>1308</v>
       </c>
       <c r="C52" t="s">
-        <v>1293</v>
+        <v>1309</v>
       </c>
       <c r="D52" t="s">
-        <v>1294</v>
+        <v>1310</v>
       </c>
       <c r="E52" t="s">
         <v>21</v>
@@ -10456,13 +12026,13 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>1295</v>
+        <v>1311</v>
       </c>
       <c r="C53" t="s">
-        <v>1296</v>
+        <v>1312</v>
       </c>
       <c r="D53" t="s">
-        <v>1297</v>
+        <v>1313</v>
       </c>
       <c r="E53" t="s">
         <v>21</v>
@@ -10477,13 +12047,13 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>1298</v>
+        <v>1314</v>
       </c>
       <c r="C54" t="s">
-        <v>1299</v>
+        <v>1315</v>
       </c>
       <c r="D54" t="s">
-        <v>1300</v>
+        <v>1316</v>
       </c>
       <c r="E54" t="s">
         <v>21</v>
@@ -10498,13 +12068,13 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>1301</v>
+        <v>1317</v>
       </c>
       <c r="C55" t="s">
-        <v>1302</v>
+        <v>1318</v>
       </c>
       <c r="D55" t="s">
-        <v>1303</v>
+        <v>1319</v>
       </c>
       <c r="E55" t="s">
         <v>21</v>
@@ -10519,13 +12089,13 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>1304</v>
+        <v>1320</v>
       </c>
       <c r="C56" t="s">
-        <v>1305</v>
+        <v>1321</v>
       </c>
       <c r="D56" t="s">
-        <v>1306</v>
+        <v>1322</v>
       </c>
       <c r="E56" t="s">
         <v>21</v>
@@ -10540,13 +12110,13 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>1307</v>
+        <v>1323</v>
       </c>
       <c r="C57" t="s">
-        <v>1308</v>
+        <v>1324</v>
       </c>
       <c r="D57" t="s">
-        <v>1309</v>
+        <v>1325</v>
       </c>
       <c r="E57" t="s">
         <v>21</v>
@@ -10561,13 +12131,13 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>1310</v>
+        <v>1326</v>
       </c>
       <c r="C58" t="s">
-        <v>1311</v>
+        <v>1327</v>
       </c>
       <c r="D58" t="s">
-        <v>1312</v>
+        <v>1328</v>
       </c>
       <c r="E58" t="s">
         <v>21</v>
@@ -10582,13 +12152,13 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>1313</v>
+        <v>1329</v>
       </c>
       <c r="C59" t="s">
-        <v>1314</v>
+        <v>1330</v>
       </c>
       <c r="D59" t="s">
-        <v>1315</v>
+        <v>1331</v>
       </c>
       <c r="E59" t="s">
         <v>21</v>
@@ -10603,13 +12173,13 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>1316</v>
+        <v>1332</v>
       </c>
       <c r="C60" t="s">
-        <v>1317</v>
+        <v>1333</v>
       </c>
       <c r="D60" t="s">
-        <v>1318</v>
+        <v>1334</v>
       </c>
       <c r="E60" t="s">
         <v>21</v>
@@ -10624,13 +12194,13 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>1319</v>
+        <v>1335</v>
       </c>
       <c r="C61" t="s">
-        <v>1320</v>
+        <v>1336</v>
       </c>
       <c r="D61" t="s">
-        <v>1321</v>
+        <v>1337</v>
       </c>
       <c r="E61" t="s">
         <v>21</v>
@@ -10645,13 +12215,13 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>1322</v>
+        <v>1338</v>
       </c>
       <c r="C62" t="s">
-        <v>1323</v>
+        <v>1339</v>
       </c>
       <c r="D62" t="s">
-        <v>1324</v>
+        <v>1340</v>
       </c>
       <c r="E62" t="s">
         <v>21</v>
@@ -10666,13 +12236,13 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>1325</v>
+        <v>1341</v>
       </c>
       <c r="C63" t="s">
-        <v>1326</v>
+        <v>1342</v>
       </c>
       <c r="D63" t="s">
-        <v>1327</v>
+        <v>1343</v>
       </c>
       <c r="E63" t="s">
         <v>21</v>
@@ -10687,13 +12257,13 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>1328</v>
+        <v>1344</v>
       </c>
       <c r="C64" t="s">
-        <v>1329</v>
+        <v>1345</v>
       </c>
       <c r="D64" t="s">
-        <v>1330</v>
+        <v>1346</v>
       </c>
       <c r="E64" t="s">
         <v>21</v>
@@ -10708,13 +12278,13 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>1331</v>
+        <v>1347</v>
       </c>
       <c r="C65" t="s">
-        <v>1332</v>
+        <v>1348</v>
       </c>
       <c r="D65" t="s">
-        <v>1333</v>
+        <v>1349</v>
       </c>
       <c r="E65" t="s">
         <v>21</v>
@@ -10729,13 +12299,13 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>1334</v>
+        <v>1350</v>
       </c>
       <c r="C66" t="s">
-        <v>1335</v>
+        <v>1351</v>
       </c>
       <c r="D66" t="s">
-        <v>1336</v>
+        <v>1352</v>
       </c>
       <c r="E66" t="s">
         <v>21</v>
@@ -10750,13 +12320,13 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>1337</v>
+        <v>1353</v>
       </c>
       <c r="C67" t="s">
-        <v>1338</v>
+        <v>1354</v>
       </c>
       <c r="D67" t="s">
-        <v>1339</v>
+        <v>1355</v>
       </c>
       <c r="E67" t="s">
         <v>21</v>
@@ -10771,13 +12341,13 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>1340</v>
+        <v>1356</v>
       </c>
       <c r="C68" t="s">
-        <v>1341</v>
+        <v>1357</v>
       </c>
       <c r="D68" t="s">
-        <v>1342</v>
+        <v>1358</v>
       </c>
       <c r="E68" t="s">
         <v>21</v>
@@ -10792,13 +12362,13 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>1343</v>
+        <v>1359</v>
       </c>
       <c r="C69" t="s">
-        <v>1344</v>
+        <v>1360</v>
       </c>
       <c r="D69" t="s">
-        <v>1345</v>
+        <v>1361</v>
       </c>
       <c r="E69" t="s">
         <v>21</v>
@@ -10813,13 +12383,13 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>1346</v>
+        <v>1362</v>
       </c>
       <c r="C70" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="D70" t="s">
-        <v>1348</v>
+        <v>1364</v>
       </c>
       <c r="E70" t="s">
         <v>21</v>
@@ -10834,13 +12404,13 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>1346</v>
+        <v>1362</v>
       </c>
       <c r="C71" t="s">
-        <v>1347</v>
+        <v>1363</v>
       </c>
       <c r="D71" t="s">
-        <v>1349</v>
+        <v>1365</v>
       </c>
       <c r="E71" t="s">
         <v>21</v>
@@ -10855,13 +12425,13 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>1350</v>
+        <v>1366</v>
       </c>
       <c r="C72" t="s">
-        <v>1351</v>
+        <v>1367</v>
       </c>
       <c r="D72" t="s">
-        <v>1352</v>
+        <v>1368</v>
       </c>
       <c r="E72" t="s">
         <v>21</v>
@@ -10876,13 +12446,13 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>1353</v>
+        <v>1369</v>
       </c>
       <c r="C73" t="s">
-        <v>1354</v>
+        <v>1370</v>
       </c>
       <c r="D73" t="s">
-        <v>1355</v>
+        <v>1371</v>
       </c>
       <c r="E73" t="s">
         <v>21</v>
@@ -10897,13 +12467,13 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>1356</v>
+        <v>1372</v>
       </c>
       <c r="C74" t="s">
-        <v>1357</v>
+        <v>1373</v>
       </c>
       <c r="D74" t="s">
-        <v>1358</v>
+        <v>1374</v>
       </c>
       <c r="E74" t="s">
         <v>21</v>
@@ -10918,13 +12488,13 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>1359</v>
+        <v>1375</v>
       </c>
       <c r="C75" t="s">
-        <v>1360</v>
+        <v>1376</v>
       </c>
       <c r="D75" t="s">
-        <v>1361</v>
+        <v>1377</v>
       </c>
       <c r="E75" t="s">
         <v>21</v>
@@ -10939,13 +12509,13 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>1362</v>
+        <v>1378</v>
       </c>
       <c r="C76" t="s">
-        <v>1363</v>
+        <v>1379</v>
       </c>
       <c r="D76" t="s">
-        <v>1364</v>
+        <v>1380</v>
       </c>
       <c r="E76" t="s">
         <v>21</v>
@@ -10959,14 +12529,2266 @@
       <c r="A77" t="n">
         <v>75</v>
       </c>
-      <c r="B77"/>
-      <c r="C77"/>
-      <c r="D77"/>
-      <c r="E77"/>
+      <c r="B77" t="s">
+        <v>1381</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1382</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1383</v>
+      </c>
+      <c r="E77" t="s">
+        <v>21</v>
+      </c>
       <c r="F77"/>
       <c r="G77"/>
       <c r="H77"/>
       <c r="I77"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1384</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1385</v>
+      </c>
+      <c r="D1" t="s">
+        <v>618</v>
+      </c>
+      <c r="E1" t="s">
+        <v>619</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1386</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1387</v>
+      </c>
+      <c r="H1" t="s">
+        <v>622</v>
+      </c>
+      <c r="I1" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="E2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="H2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="I2" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1396</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1397</v>
+      </c>
+      <c r="D3" t="s">
+        <v>1398</v>
+      </c>
+      <c r="E3" t="s">
+        <v>1399</v>
+      </c>
+      <c r="F3" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G3" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H3" t="s">
+        <v>1402</v>
+      </c>
+      <c r="I3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1403</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1404</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="E4" t="s">
+        <v>53</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1407</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="I4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1409</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1410</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1411</v>
+      </c>
+      <c r="E5" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1412</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1414</v>
+      </c>
+      <c r="I5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1415</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1416</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1417</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1419</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1421</v>
+      </c>
+      <c r="I6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1424</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1429</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1430</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1431</v>
+      </c>
+      <c r="E8" t="s">
+        <v>643</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1432</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1433</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1435</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1437</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1438</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1439</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1440</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1441</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1442</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1443</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1444</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1445</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1447</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1449</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1451</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1452</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1453</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1455</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1456</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1456</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1458</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1459</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1460</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1461</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1464</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1466</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1467</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1469</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1470</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1471</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1472</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1474</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1478</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1480</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1481</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1482</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1483</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1485</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1488</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1489</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1494</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1495</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1496</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1500</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1501</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1502</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1504</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1507</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1508</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1508</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1511</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1512</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1513</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1514</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1515</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1516</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1517</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1520</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1522</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1523</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1524</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1525</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1526</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1527</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1528</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1531</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1532</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1533</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1534</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1535</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1538</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1539</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1541</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1542</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1543</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1544</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1545</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1545</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1547</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1550</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1551</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1552</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1553</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1556</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1557</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1558</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1560</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1561</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1564</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1565</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1568</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1569</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1570</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1570</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1571</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1572</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1574</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1576</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1577</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1579</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1580</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1581</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1583</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1586</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1587</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1588</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1589</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1590</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1591</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1593</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1594</v>
+      </c>
+      <c r="I32" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1595</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1597</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1598</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1599</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1600</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1602</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1604</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1605</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1605</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1610</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1612</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1614</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1615</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1617</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1619</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1620</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1621</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1622</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1623</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1624</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1625</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1627</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1628</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1629</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1630</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1631</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1632</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1633</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1634</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1635</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1636</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1637</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1638</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1639</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1640</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1641</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1642</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1643</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1644</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1645</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1646</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1647</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1648</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1649</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1650</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1651</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1652</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1653</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1654</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1655</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1656</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1658</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1659</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1660</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1661</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1662</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1663</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1664</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1665</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1666</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1667</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1668</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1668</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1509</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1669</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1670</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1671</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1672</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1673</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1674</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1675</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1676</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1677</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1679</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1680</v>
+      </c>
+      <c r="I46" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1681</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1682</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1683</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1684</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1685</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1686</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1687</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1688</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1689</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1690</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1691</v>
+      </c>
+      <c r="H48" t="s">
+        <v>1692</v>
+      </c>
+      <c r="I48" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1693</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1694</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1695</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1450</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1696</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1697</v>
+      </c>
+      <c r="H49" t="s">
+        <v>1698</v>
+      </c>
+      <c r="I49" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1699</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1700</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1701</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1702</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1703</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1704</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1705</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1707</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1709</v>
+      </c>
+      <c r="H51" t="s">
+        <v>1710</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1711</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1712</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1713</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1714</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1715</v>
+      </c>
+      <c r="H52" t="s">
+        <v>1715</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1716</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1717</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1718</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1719</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1720</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1721</v>
+      </c>
+      <c r="I53" t="s">
+        <v>1722</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1727</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1728</v>
+      </c>
+      <c r="I54" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1729</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1730</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1731</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1732</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1733</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1734</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1735</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1736</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1737</v>
+      </c>
+      <c r="E56" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1738</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1739</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1740</v>
+      </c>
+      <c r="I56" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1741</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1742</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1743</v>
+      </c>
+      <c r="E57" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1745</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1746</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1747</v>
+      </c>
+      <c r="I57" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1748</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1749</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1750</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1751</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1752</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1753</v>
+      </c>
+      <c r="I58" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1754</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1755</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1756</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1757</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1758</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1759</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1760</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1761</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1762</v>
+      </c>
+      <c r="E60" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1763</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1765</v>
+      </c>
+      <c r="I60" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1766</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1767</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1768</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F61" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1771</v>
+      </c>
+      <c r="I61" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1772</v>
+      </c>
+      <c r="C62" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D62" t="s">
+        <v>1774</v>
+      </c>
+      <c r="E62" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1775</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1776</v>
+      </c>
+      <c r="H62" t="s">
+        <v>1777</v>
+      </c>
+      <c r="I62" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1778</v>
+      </c>
+      <c r="C63" t="s">
+        <v>1779</v>
+      </c>
+      <c r="D63" t="s">
+        <v>1780</v>
+      </c>
+      <c r="E63" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F63" t="s">
+        <v>1781</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1782</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1783</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C64" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D64" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E64" t="s">
+        <v>1391</v>
+      </c>
+      <c r="F64" t="s">
+        <v>1787</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1788</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1788</v>
+      </c>
+      <c r="I64" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C65" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D65" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E65" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F65" t="s">
+        <v>1792</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1793</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1794</v>
+      </c>
+      <c r="I65" t="s">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C66" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D66" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E66" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F66" t="s">
+        <v>1798</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1799</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1800</v>
+      </c>
+      <c r="I66" t="s">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1801</v>
+      </c>
+      <c r="C67" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D67" t="s">
+        <v>1803</v>
+      </c>
+      <c r="E67" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1805</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1806</v>
+      </c>
+      <c r="I67" t="s">
+        <v>1450</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1807</v>
+      </c>
+      <c r="C68" t="s">
+        <v>1808</v>
+      </c>
+      <c r="D68" t="s">
+        <v>1809</v>
+      </c>
+      <c r="E68" t="s">
+        <v>1499</v>
+      </c>
+      <c r="F68" t="s">
+        <v>1810</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1811</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1812</v>
+      </c>
+      <c r="I68" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1813</v>
+      </c>
+      <c r="C69" t="s">
+        <v>1814</v>
+      </c>
+      <c r="D69" t="s">
+        <v>1815</v>
+      </c>
+      <c r="E69" t="s">
+        <v>1744</v>
+      </c>
+      <c r="F69" t="s">
+        <v>1816</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1817</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1818</v>
+      </c>
+      <c r="I69" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1819</v>
+      </c>
+      <c r="C70" t="s">
+        <v>1820</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1821</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F70" t="s">
+        <v>1823</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1824</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1825</v>
+      </c>
+      <c r="I70" t="s">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1826</v>
+      </c>
+      <c r="C71" t="s">
+        <v>1827</v>
+      </c>
+      <c r="D71" t="s">
+        <v>1828</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1822</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1829</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1830</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1831</v>
+      </c>
+      <c r="I71" t="s">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C72" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D72" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E72" t="s">
+        <v>38</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1835</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1836</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1837</v>
+      </c>
+      <c r="I72" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="s">
+        <v>574</v>
+      </c>
+      <c r="C73" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D73" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E73" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F73" t="s">
+        <v>578</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1841</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1842</v>
+      </c>
+      <c r="I73" t="s">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1844</v>
+      </c>
+      <c r="C74" t="s">
+        <v>1845</v>
+      </c>
+      <c r="D74" t="s">
+        <v>1846</v>
+      </c>
+      <c r="E74" t="s">
+        <v>1847</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1848</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1849</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1850</v>
+      </c>
+      <c r="I74" t="s">
+        <v>1851</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1852</v>
+      </c>
+      <c r="C75" t="s">
+        <v>1853</v>
+      </c>
+      <c r="D75" t="s">
+        <v>1854</v>
+      </c>
+      <c r="E75" t="s">
+        <v>1855</v>
+      </c>
+      <c r="F75" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1857</v>
+      </c>
+      <c r="H75" t="s">
+        <v>1858</v>
+      </c>
+      <c r="I75" t="s">
+        <v>1859</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C76" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D76" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E76" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1864</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1865</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1866</v>
+      </c>
+      <c r="I76" t="s">
+        <v>1867</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1868</v>
+      </c>
+      <c r="C77" t="s">
+        <v>1869</v>
+      </c>
+      <c r="D77" t="s">
+        <v>1870</v>
+      </c>
+      <c r="E77" t="s">
+        <v>1871</v>
+      </c>
+      <c r="F77" t="s">
+        <v>1872</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1873</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1874</v>
+      </c>
+      <c r="I77" t="s">
+        <v>1875</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
